--- a/data/MK_ECB_DATA_20260617.xlsx
+++ b/data/MK_ECB_DATA_20260617.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E315"/>
+  <dimension ref="A1:E318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,25 +1193,25 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2QQF32.CR</t>
+          <t>EST.B.EU000A2QQF24.CR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>€STR 3개월 복리평균</t>
+          <t>€STR 1개월 복리평균</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.93597</v>
+        <v>1.93243</v>
       </c>
     </row>
     <row r="35">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1253,11 +1253,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.93598</v>
+        <v>1.93597</v>
       </c>
     </row>
     <row r="37">
@@ -1276,11 +1276,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.93603</v>
+        <v>1.93598</v>
       </c>
     </row>
     <row r="38">
@@ -1299,11 +1299,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.93607</v>
+        <v>1.93603</v>
       </c>
     </row>
     <row r="39">
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.93597</v>
+        <v>1.93607</v>
       </c>
     </row>
     <row r="40">
@@ -1345,11 +1345,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.93598</v>
+        <v>1.93597</v>
       </c>
     </row>
     <row r="41">
@@ -1368,11 +1368,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.93596</v>
+        <v>1.93598</v>
       </c>
     </row>
     <row r="42">
@@ -1391,11 +1391,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.93597</v>
+        <v>1.93596</v>
       </c>
     </row>
     <row r="43">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.93601</v>
+        <v>1.93597</v>
       </c>
     </row>
     <row r="44">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.93597</v>
+        <v>1.93601</v>
       </c>
     </row>
     <row r="45">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1483,11 +1483,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.93592</v>
+        <v>1.93597</v>
       </c>
     </row>
     <row r="47">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.93597</v>
+        <v>1.93592</v>
       </c>
     </row>
     <row r="48">
@@ -1529,11 +1529,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.93603</v>
+        <v>1.93597</v>
       </c>
     </row>
     <row r="49">
@@ -1552,11 +1552,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1.93582</v>
+        <v>1.93603</v>
       </c>
     </row>
     <row r="50">
@@ -1575,11 +1575,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1.9358</v>
+        <v>1.93582</v>
       </c>
     </row>
     <row r="51">
@@ -1598,11 +1598,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1.93577</v>
+        <v>1.9358</v>
       </c>
     </row>
     <row r="52">
@@ -1621,11 +1621,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.93583</v>
+        <v>1.93577</v>
       </c>
     </row>
     <row r="53">
@@ -1644,11 +1644,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.9359</v>
+        <v>1.93583</v>
       </c>
     </row>
     <row r="54">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1690,11 +1690,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.93595</v>
+        <v>1.9359</v>
       </c>
     </row>
     <row r="56">
@@ -1713,11 +1713,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.93593</v>
+        <v>1.93595</v>
       </c>
     </row>
     <row r="57">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1.93589</v>
+        <v>1.93593</v>
       </c>
     </row>
     <row r="58">
@@ -1759,11 +1759,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.93588</v>
+        <v>1.93589</v>
       </c>
     </row>
     <row r="59">
@@ -1782,11 +1782,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.93594</v>
+        <v>1.93588</v>
       </c>
     </row>
     <row r="60">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1.93576</v>
+        <v>1.93594</v>
       </c>
     </row>
     <row r="61">
@@ -1828,11 +1828,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.93574</v>
+        <v>1.93576</v>
       </c>
     </row>
     <row r="62">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.93571</v>
+        <v>1.93574</v>
       </c>
     </row>
     <row r="63">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -1897,11 +1897,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.9358</v>
+        <v>1.93571</v>
       </c>
     </row>
     <row r="65">
@@ -1920,57 +1920,57 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.93573</v>
+        <v>1.9358</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2X2A25.WT</t>
+          <t>EST.B.EU000A2QQF32.CR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>€STR 금리</t>
+          <t>€STR 3개월 복리평균</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.932</v>
+        <v>1.93573</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2X2A25.WT</t>
+          <t>EST.B.EU000A2QQF32.CR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>€STR 금리</t>
+          <t>€STR 3개월 복리평균</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1.932</v>
+        <v>1.93572</v>
       </c>
     </row>
     <row r="68">
@@ -1989,11 +1989,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1.931</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="69">
@@ -2012,11 +2012,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1.93</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="70">
@@ -2035,11 +2035,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.929</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="71">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1.931</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="72">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2104,11 +2104,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1.928</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="74">
@@ -2127,11 +2127,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1.93</v>
+        <v>1.929</v>
       </c>
     </row>
     <row r="75">
@@ -2150,11 +2150,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.931</v>
+        <v>1.928</v>
       </c>
     </row>
     <row r="76">
@@ -2173,11 +2173,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1.931</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="77">
@@ -2196,11 +2196,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1.929</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="78">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2242,11 +2242,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1.932</v>
+        <v>1.929</v>
       </c>
     </row>
     <row r="80">
@@ -2265,11 +2265,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.929</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="81">
@@ -2288,11 +2288,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.931</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="82">
@@ -2311,11 +2311,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.932</v>
+        <v>1.929</v>
       </c>
     </row>
     <row r="83">
@@ -2334,11 +2334,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.932</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="84">
@@ -2357,11 +2357,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.933</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="85">
@@ -2380,11 +2380,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.93</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="86">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1.931</v>
+        <v>1.933</v>
       </c>
     </row>
     <row r="87">
@@ -2426,11 +2426,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.932</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="88">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2472,11 +2472,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.933</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="90">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2518,11 +2518,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.93</v>
+        <v>1.933</v>
       </c>
     </row>
     <row r="92">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1.93</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="93">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2587,11 +2587,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1.931</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="95">
@@ -2610,11 +2610,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1.931</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="96">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2665,48 +2665,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2QQF08.CI</t>
+          <t>EST.B.EU000A2X2A25.WT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>€STR 복리지수</t>
+          <t>€STR 금리</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>108.924487</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2QQF08.CI</t>
+          <t>EST.B.EU000A2X2A25.WT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>€STR 복리지수</t>
+          <t>€STR 금리</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>108.930332</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="100">
@@ -2725,11 +2725,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>108.936178</v>
+        <v>108.924487</v>
       </c>
     </row>
     <row r="101">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>108.942021</v>
+        <v>108.930332</v>
       </c>
     </row>
     <row r="102">
@@ -2771,11 +2771,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>108.947862</v>
+        <v>108.936178</v>
       </c>
     </row>
     <row r="103">
@@ -2794,11 +2794,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>108.965375</v>
+        <v>108.942021</v>
       </c>
     </row>
     <row r="104">
@@ -2817,11 +2817,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>108.97122</v>
+        <v>108.947862</v>
       </c>
     </row>
     <row r="105">
@@ -2840,11 +2840,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>108.977059</v>
+        <v>108.965375</v>
       </c>
     </row>
     <row r="106">
@@ -2863,11 +2863,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>108.982895</v>
+        <v>108.97122</v>
       </c>
     </row>
     <row r="107">
@@ -2886,11 +2886,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>108.988738</v>
+        <v>108.977059</v>
       </c>
     </row>
     <row r="108">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>109.006276</v>
+        <v>108.982895</v>
       </c>
     </row>
     <row r="109">
@@ -2932,11 +2932,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>109.012123</v>
+        <v>108.988738</v>
       </c>
     </row>
     <row r="110">
@@ -2955,11 +2955,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>109.017964</v>
+        <v>109.006276</v>
       </c>
     </row>
     <row r="111">
@@ -2978,11 +2978,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>109.023812</v>
+        <v>109.012123</v>
       </c>
     </row>
     <row r="112">
@@ -3001,11 +3001,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>109.029663</v>
+        <v>109.017964</v>
       </c>
     </row>
     <row r="113">
@@ -3024,11 +3024,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>109.047189</v>
+        <v>109.023812</v>
       </c>
     </row>
     <row r="114">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>109.053039</v>
+        <v>109.029663</v>
       </c>
     </row>
     <row r="115">
@@ -3070,11 +3070,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>109.058891</v>
+        <v>109.047189</v>
       </c>
     </row>
     <row r="116">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>109.064744</v>
+        <v>109.053039</v>
       </c>
     </row>
     <row r="117">
@@ -3116,11 +3116,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>109.0706</v>
+        <v>109.058891</v>
       </c>
     </row>
     <row r="118">
@@ -3139,11 +3139,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>109.088142</v>
+        <v>109.064744</v>
       </c>
     </row>
     <row r="119">
@@ -3162,11 +3162,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>109.093994</v>
+        <v>109.0706</v>
       </c>
     </row>
     <row r="120">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>109.099848</v>
+        <v>109.088142</v>
       </c>
     </row>
     <row r="121">
@@ -3208,11 +3208,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>109.1057</v>
+        <v>109.093994</v>
       </c>
     </row>
     <row r="122">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>109.111559</v>
+        <v>109.099848</v>
       </c>
     </row>
     <row r="123">
@@ -3254,11 +3254,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>109.129117</v>
+        <v>109.1057</v>
       </c>
     </row>
     <row r="124">
@@ -3277,11 +3277,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>109.134967</v>
+        <v>109.111559</v>
       </c>
     </row>
     <row r="125">
@@ -3300,11 +3300,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>109.140818</v>
+        <v>109.129117</v>
       </c>
     </row>
     <row r="126">
@@ -3323,11 +3323,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>109.146669</v>
+        <v>109.134967</v>
       </c>
     </row>
     <row r="127">
@@ -3346,11 +3346,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>109.152524</v>
+        <v>109.140818</v>
       </c>
     </row>
     <row r="128">
@@ -3369,11 +3369,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>109.170088</v>
+        <v>109.146669</v>
       </c>
     </row>
     <row r="129">
@@ -3392,80 +3392,80 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>109.175944</v>
+        <v>109.152524</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
+          <t>EST.B.EU000A2QQF08.CI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>유로존 국채금리 1년</t>
+          <t>€STR 복리지수</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2.604738</v>
+        <v>109.170088</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
+          <t>EST.B.EU000A2QQF08.CI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>유로존 국채금리 1년</t>
+          <t>€STR 복리지수</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2.602065</v>
+        <v>109.175944</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
+          <t>EST.B.EU000A2QQF08.CI</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>유로존 국채금리 1년</t>
+          <t>€STR 복리지수</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2.50443</v>
+        <v>109.1818</v>
       </c>
     </row>
     <row r="133">
@@ -3484,11 +3484,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2.488514</v>
+        <v>2.604738</v>
       </c>
     </row>
     <row r="134">
@@ -3507,11 +3507,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2.514596</v>
+        <v>2.602065</v>
       </c>
     </row>
     <row r="135">
@@ -3530,11 +3530,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2.553344</v>
+        <v>2.50443</v>
       </c>
     </row>
     <row r="136">
@@ -3553,11 +3553,11 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2.600826</v>
+        <v>2.488514</v>
       </c>
     </row>
     <row r="137">
@@ -3576,11 +3576,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2.594349</v>
+        <v>2.514596</v>
       </c>
     </row>
     <row r="138">
@@ -3599,11 +3599,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2.57128</v>
+        <v>2.553344</v>
       </c>
     </row>
     <row r="139">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2.617938</v>
+        <v>2.600826</v>
       </c>
     </row>
     <row r="140">
@@ -3645,11 +3645,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2.580883</v>
+        <v>2.594349</v>
       </c>
     </row>
     <row r="141">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2.606135</v>
+        <v>2.57128</v>
       </c>
     </row>
     <row r="142">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2.593521</v>
+        <v>2.617938</v>
       </c>
     </row>
     <row r="143">
@@ -3714,11 +3714,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2.574793</v>
+        <v>2.580883</v>
       </c>
     </row>
     <row r="144">
@@ -3737,11 +3737,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2.535177</v>
+        <v>2.606135</v>
       </c>
     </row>
     <row r="145">
@@ -3760,11 +3760,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2.462774</v>
+        <v>2.593521</v>
       </c>
     </row>
     <row r="146">
@@ -3783,11 +3783,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2.50502</v>
+        <v>2.574793</v>
       </c>
     </row>
     <row r="147">
@@ -3806,11 +3806,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2.500937</v>
+        <v>2.535177</v>
       </c>
     </row>
     <row r="148">
@@ -3829,11 +3829,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2.526205</v>
+        <v>2.462774</v>
       </c>
     </row>
     <row r="149">
@@ -3852,11 +3852,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2.500537</v>
+        <v>2.50502</v>
       </c>
     </row>
     <row r="150">
@@ -3875,11 +3875,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2.577046</v>
+        <v>2.500937</v>
       </c>
     </row>
     <row r="151">
@@ -3898,11 +3898,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2.558293</v>
+        <v>2.526205</v>
       </c>
     </row>
     <row r="152">
@@ -3921,11 +3921,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2.579685</v>
+        <v>2.500537</v>
       </c>
     </row>
     <row r="153">
@@ -3944,11 +3944,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2.575429</v>
+        <v>2.577046</v>
       </c>
     </row>
     <row r="154">
@@ -3967,11 +3967,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2.595465</v>
+        <v>2.558293</v>
       </c>
     </row>
     <row r="155">
@@ -3990,11 +3990,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2.610515</v>
+        <v>2.579685</v>
       </c>
     </row>
     <row r="156">
@@ -4013,11 +4013,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2.599927</v>
+        <v>2.575429</v>
       </c>
     </row>
     <row r="157">
@@ -4036,11 +4036,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2.623955</v>
+        <v>2.595465</v>
       </c>
     </row>
     <row r="158">
@@ -4059,11 +4059,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2.615212</v>
+        <v>2.610515</v>
       </c>
     </row>
     <row r="159">
@@ -4082,11 +4082,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2.576759</v>
+        <v>2.599927</v>
       </c>
     </row>
     <row r="160">
@@ -4105,80 +4105,80 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2.527404</v>
+        <v>2.623955</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2.709578</v>
+        <v>2.615212</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2.713377</v>
+        <v>2.576759</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2.580816</v>
+        <v>2.527404</v>
       </c>
     </row>
     <row r="164">
@@ -4197,11 +4197,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2.563197</v>
+        <v>2.709578</v>
       </c>
     </row>
     <row r="165">
@@ -4220,11 +4220,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2.590769</v>
+        <v>2.713377</v>
       </c>
     </row>
     <row r="166">
@@ -4243,11 +4243,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2.651872</v>
+        <v>2.580816</v>
       </c>
     </row>
     <row r="167">
@@ -4266,11 +4266,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2.734067</v>
+        <v>2.563197</v>
       </c>
     </row>
     <row r="168">
@@ -4289,11 +4289,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2.720401</v>
+        <v>2.590769</v>
       </c>
     </row>
     <row r="169">
@@ -4312,11 +4312,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2.673633</v>
+        <v>2.651872</v>
       </c>
     </row>
     <row r="170">
@@ -4335,11 +4335,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2.759799</v>
+        <v>2.734067</v>
       </c>
     </row>
     <row r="171">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2.701019</v>
+        <v>2.720401</v>
       </c>
     </row>
     <row r="172">
@@ -4381,11 +4381,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2.758581</v>
+        <v>2.673633</v>
       </c>
     </row>
     <row r="173">
@@ -4404,11 +4404,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2.732917</v>
+        <v>2.759799</v>
       </c>
     </row>
     <row r="174">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2.690643</v>
+        <v>2.701019</v>
       </c>
     </row>
     <row r="175">
@@ -4450,11 +4450,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2.649058</v>
+        <v>2.758581</v>
       </c>
     </row>
     <row r="176">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2.550151</v>
+        <v>2.732917</v>
       </c>
     </row>
     <row r="177">
@@ -4496,11 +4496,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2.600158</v>
+        <v>2.690643</v>
       </c>
     </row>
     <row r="178">
@@ -4519,11 +4519,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2.584193</v>
+        <v>2.649058</v>
       </c>
     </row>
     <row r="179">
@@ -4542,11 +4542,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2.60767</v>
+        <v>2.550151</v>
       </c>
     </row>
     <row r="180">
@@ -4565,11 +4565,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2.573921</v>
+        <v>2.600158</v>
       </c>
     </row>
     <row r="181">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2.664843</v>
+        <v>2.584193</v>
       </c>
     </row>
     <row r="182">
@@ -4611,11 +4611,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2.631211</v>
+        <v>2.60767</v>
       </c>
     </row>
     <row r="183">
@@ -4634,11 +4634,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2.668913</v>
+        <v>2.573921</v>
       </c>
     </row>
     <row r="184">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2.667137</v>
+        <v>2.664843</v>
       </c>
     </row>
     <row r="185">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2.690449</v>
+        <v>2.631211</v>
       </c>
     </row>
     <row r="186">
@@ -4703,11 +4703,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2.70087</v>
+        <v>2.668913</v>
       </c>
     </row>
     <row r="187">
@@ -4726,11 +4726,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2.687806</v>
+        <v>2.667137</v>
       </c>
     </row>
     <row r="188">
@@ -4749,11 +4749,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2.718796</v>
+        <v>2.690449</v>
       </c>
     </row>
     <row r="189">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2.687187</v>
+        <v>2.70087</v>
       </c>
     </row>
     <row r="190">
@@ -4795,11 +4795,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2.661527</v>
+        <v>2.687806</v>
       </c>
     </row>
     <row r="191">
@@ -4818,80 +4818,80 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2.585514</v>
+        <v>2.718796</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2.785695</v>
+        <v>2.687187</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2.791931</v>
+        <v>2.661527</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2.660543</v>
+        <v>2.585514</v>
       </c>
     </row>
     <row r="195">
@@ -4910,11 +4910,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2.647172</v>
+        <v>2.785695</v>
       </c>
     </row>
     <row r="196">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2.668906</v>
+        <v>2.791931</v>
       </c>
     </row>
     <row r="197">
@@ -4956,11 +4956,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2.727433</v>
+        <v>2.660543</v>
       </c>
     </row>
     <row r="198">
@@ -4979,11 +4979,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2.812236</v>
+        <v>2.647172</v>
       </c>
     </row>
     <row r="199">
@@ -5002,11 +5002,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2.800452</v>
+        <v>2.668906</v>
       </c>
     </row>
     <row r="200">
@@ -5025,11 +5025,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2.746714</v>
+        <v>2.727433</v>
       </c>
     </row>
     <row r="201">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2.846863</v>
+        <v>2.812236</v>
       </c>
     </row>
     <row r="202">
@@ -5071,11 +5071,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2.787952</v>
+        <v>2.800452</v>
       </c>
     </row>
     <row r="203">
@@ -5094,11 +5094,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2.854181</v>
+        <v>2.746714</v>
       </c>
     </row>
     <row r="204">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2.823594</v>
+        <v>2.846863</v>
       </c>
     </row>
     <row r="205">
@@ -5140,11 +5140,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2.775414</v>
+        <v>2.787952</v>
       </c>
     </row>
     <row r="206">
@@ -5163,11 +5163,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>2.73301</v>
+        <v>2.854181</v>
       </c>
     </row>
     <row r="207">
@@ -5186,11 +5186,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2.632702</v>
+        <v>2.823594</v>
       </c>
     </row>
     <row r="208">
@@ -5209,11 +5209,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>2.685019</v>
+        <v>2.775414</v>
       </c>
     </row>
     <row r="209">
@@ -5232,11 +5232,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>2.665718</v>
+        <v>2.73301</v>
       </c>
     </row>
     <row r="210">
@@ -5255,11 +5255,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2.685927</v>
+        <v>2.632702</v>
       </c>
     </row>
     <row r="211">
@@ -5278,11 +5278,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2.653732</v>
+        <v>2.685019</v>
       </c>
     </row>
     <row r="212">
@@ -5301,11 +5301,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2.737626</v>
+        <v>2.665718</v>
       </c>
     </row>
     <row r="213">
@@ -5324,11 +5324,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>2.695968</v>
+        <v>2.685927</v>
       </c>
     </row>
     <row r="214">
@@ -5347,11 +5347,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2.739566</v>
+        <v>2.653732</v>
       </c>
     </row>
     <row r="215">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>2.742955</v>
+        <v>2.737626</v>
       </c>
     </row>
     <row r="216">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>2.76777</v>
+        <v>2.695968</v>
       </c>
     </row>
     <row r="217">
@@ -5416,11 +5416,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>2.775779</v>
+        <v>2.739566</v>
       </c>
     </row>
     <row r="218">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>2.765536</v>
+        <v>2.742955</v>
       </c>
     </row>
     <row r="219">
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>2.79679</v>
+        <v>2.76777</v>
       </c>
     </row>
     <row r="220">
@@ -5485,11 +5485,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>2.759517</v>
+        <v>2.775779</v>
       </c>
     </row>
     <row r="221">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2.740071</v>
+        <v>2.765536</v>
       </c>
     </row>
     <row r="222">
@@ -5531,80 +5531,80 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>2.664179</v>
+        <v>2.79679</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>3.000517</v>
+        <v>2.759517</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>3.007991</v>
+        <v>2.740071</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2.886073</v>
+        <v>2.664179</v>
       </c>
     </row>
     <row r="226">
@@ -5623,11 +5623,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2.876206</v>
+        <v>3.000517</v>
       </c>
     </row>
     <row r="227">
@@ -5646,11 +5646,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2.889313</v>
+        <v>3.007991</v>
       </c>
     </row>
     <row r="228">
@@ -5669,11 +5669,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2.939157</v>
+        <v>2.886073</v>
       </c>
     </row>
     <row r="229">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>3.015143</v>
+        <v>2.876206</v>
       </c>
     </row>
     <row r="230">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>3.012751</v>
+        <v>2.889313</v>
       </c>
     </row>
     <row r="231">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2.955911</v>
+        <v>2.939157</v>
       </c>
     </row>
     <row r="232">
@@ -5761,11 +5761,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>3.063218</v>
+        <v>3.015143</v>
       </c>
     </row>
     <row r="233">
@@ -5784,11 +5784,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>3.014232</v>
+        <v>3.012751</v>
       </c>
     </row>
     <row r="234">
@@ -5807,11 +5807,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>3.077971</v>
+        <v>2.955911</v>
       </c>
     </row>
     <row r="235">
@@ -5830,11 +5830,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>3.044699</v>
+        <v>3.063218</v>
       </c>
     </row>
     <row r="236">
@@ -5853,11 +5853,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>2.995816</v>
+        <v>3.014232</v>
       </c>
     </row>
     <row r="237">
@@ -5876,11 +5876,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>2.948017</v>
+        <v>3.077971</v>
       </c>
     </row>
     <row r="238">
@@ -5899,11 +5899,11 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>2.848562</v>
+        <v>3.044699</v>
       </c>
     </row>
     <row r="239">
@@ -5922,11 +5922,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2.900503</v>
+        <v>2.995816</v>
       </c>
     </row>
     <row r="240">
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2.881685</v>
+        <v>2.948017</v>
       </c>
     </row>
     <row r="241">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2.899034</v>
+        <v>2.848562</v>
       </c>
     </row>
     <row r="242">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>2.869598</v>
+        <v>2.900503</v>
       </c>
     </row>
     <row r="243">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2.942888</v>
+        <v>2.881685</v>
       </c>
     </row>
     <row r="244">
@@ -6037,11 +6037,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>2.892125</v>
+        <v>2.899034</v>
       </c>
     </row>
     <row r="245">
@@ -6060,11 +6060,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2.936988</v>
+        <v>2.869598</v>
       </c>
     </row>
     <row r="246">
@@ -6083,11 +6083,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>2.946672</v>
+        <v>2.942888</v>
       </c>
     </row>
     <row r="247">
@@ -6106,11 +6106,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>2.97218</v>
+        <v>2.892125</v>
       </c>
     </row>
     <row r="248">
@@ -6129,11 +6129,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>2.981788</v>
+        <v>2.936988</v>
       </c>
     </row>
     <row r="249">
@@ -6152,11 +6152,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>2.976278</v>
+        <v>2.946672</v>
       </c>
     </row>
     <row r="250">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>3.004347</v>
+        <v>2.97218</v>
       </c>
     </row>
     <row r="251">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2.965561</v>
+        <v>2.981788</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2.949891</v>
+        <v>2.976278</v>
       </c>
     </row>
     <row r="253">
@@ -6244,80 +6244,80 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2.878033</v>
+        <v>3.004347</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>3.228543</v>
+        <v>2.965561</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>3.237712</v>
+        <v>2.949891</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>3.119151</v>
+        <v>2.878033</v>
       </c>
     </row>
     <row r="257">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>3.108997</v>
+        <v>3.228543</v>
       </c>
     </row>
     <row r="258">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3.118124</v>
+        <v>3.237712</v>
       </c>
     </row>
     <row r="259">
@@ -6382,11 +6382,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>3.16475</v>
+        <v>3.119151</v>
       </c>
     </row>
     <row r="260">
@@ -6405,11 +6405,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3.237417</v>
+        <v>3.108997</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3.240594</v>
+        <v>3.118124</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>3.18189</v>
+        <v>3.16475</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>3.292831</v>
+        <v>3.237417</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>3.250782</v>
+        <v>3.240594</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3.311581</v>
+        <v>3.18189</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3.275978</v>
+        <v>3.292831</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>3.226414</v>
+        <v>3.250782</v>
       </c>
     </row>
     <row r="268">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>3.172951</v>
+        <v>3.311581</v>
       </c>
     </row>
     <row r="269">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3.070373</v>
+        <v>3.275978</v>
       </c>
     </row>
     <row r="270">
@@ -6635,11 +6635,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>3.121809</v>
+        <v>3.226414</v>
       </c>
     </row>
     <row r="271">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>3.104055</v>
+        <v>3.172951</v>
       </c>
     </row>
     <row r="272">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>3.12121</v>
+        <v>3.070373</v>
       </c>
     </row>
     <row r="273">
@@ -6704,11 +6704,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>3.091758</v>
+        <v>3.121809</v>
       </c>
     </row>
     <row r="274">
@@ -6727,11 +6727,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>3.162397</v>
+        <v>3.104055</v>
       </c>
     </row>
     <row r="275">
@@ -6750,11 +6750,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>3.105972</v>
+        <v>3.12121</v>
       </c>
     </row>
     <row r="276">
@@ -6773,11 +6773,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3.150735</v>
+        <v>3.091758</v>
       </c>
     </row>
     <row r="277">
@@ -6796,11 +6796,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>3.164004</v>
+        <v>3.162397</v>
       </c>
     </row>
     <row r="278">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>3.188864</v>
+        <v>3.105972</v>
       </c>
     </row>
     <row r="279">
@@ -6842,11 +6842,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>3.200686</v>
+        <v>3.150735</v>
       </c>
     </row>
     <row r="280">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>3.197992</v>
+        <v>3.164004</v>
       </c>
     </row>
     <row r="281">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>3.223329</v>
+        <v>3.188864</v>
       </c>
     </row>
     <row r="282">
@@ -6911,11 +6911,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>3.182662</v>
+        <v>3.200686</v>
       </c>
     </row>
     <row r="283">
@@ -6934,11 +6934,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>3.16864</v>
+        <v>3.197992</v>
       </c>
     </row>
     <row r="284">
@@ -6957,80 +6957,80 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>3.096218</v>
+        <v>3.223329</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3.522383</v>
+        <v>3.182662</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>3.53446</v>
+        <v>3.16864</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>3.419526</v>
+        <v>3.096218</v>
       </c>
     </row>
     <row r="288">
@@ -7049,11 +7049,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>3.407866</v>
+        <v>3.522383</v>
       </c>
     </row>
     <row r="289">
@@ -7072,11 +7072,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>3.414486</v>
+        <v>3.53446</v>
       </c>
     </row>
     <row r="290">
@@ -7095,11 +7095,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>3.459084</v>
+        <v>3.419526</v>
       </c>
     </row>
     <row r="291">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3.532267</v>
+        <v>3.407866</v>
       </c>
     </row>
     <row r="292">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>3.537955</v>
+        <v>3.414486</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>3.477861</v>
+        <v>3.459084</v>
       </c>
     </row>
     <row r="294">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>3.591227</v>
+        <v>3.532267</v>
       </c>
     </row>
     <row r="295">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>3.555828</v>
+        <v>3.537955</v>
       </c>
     </row>
     <row r="296">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>3.614122</v>
+        <v>3.477861</v>
       </c>
     </row>
     <row r="297">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>3.57531</v>
+        <v>3.591227</v>
       </c>
     </row>
     <row r="298">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3.524301</v>
+        <v>3.555828</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>3.465361</v>
+        <v>3.614122</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>3.358616</v>
+        <v>3.57531</v>
       </c>
     </row>
     <row r="301">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>3.408954</v>
+        <v>3.524301</v>
       </c>
     </row>
     <row r="302">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>3.392661</v>
+        <v>3.465361</v>
       </c>
     </row>
     <row r="303">
@@ -7394,11 +7394,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>3.410886</v>
+        <v>3.358616</v>
       </c>
     </row>
     <row r="304">
@@ -7417,11 +7417,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>3.380955</v>
+        <v>3.408954</v>
       </c>
     </row>
     <row r="305">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>3.450091</v>
+        <v>3.392661</v>
       </c>
     </row>
     <row r="306">
@@ -7463,11 +7463,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>3.390251</v>
+        <v>3.410886</v>
       </c>
     </row>
     <row r="307">
@@ -7486,11 +7486,11 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>3.434872</v>
+        <v>3.380955</v>
       </c>
     </row>
     <row r="308">
@@ -7509,11 +7509,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>3.451103</v>
+        <v>3.450091</v>
       </c>
     </row>
     <row r="309">
@@ -7532,11 +7532,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>3.474414</v>
+        <v>3.390251</v>
       </c>
     </row>
     <row r="310">
@@ -7555,11 +7555,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3.487726</v>
+        <v>3.434872</v>
       </c>
     </row>
     <row r="311">
@@ -7578,11 +7578,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>3.488064</v>
+        <v>3.451103</v>
       </c>
     </row>
     <row r="312">
@@ -7601,11 +7601,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>3.510348</v>
+        <v>3.474414</v>
       </c>
     </row>
     <row r="313">
@@ -7624,11 +7624,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>3.466867</v>
+        <v>3.487726</v>
       </c>
     </row>
     <row r="314">
@@ -7647,11 +7647,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>3.45513</v>
+        <v>3.488064</v>
       </c>
     </row>
     <row r="315">
@@ -7670,10 +7670,79 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>3.510348</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>10</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>3.466867</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>10</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>3.45513</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>10</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
           <t>20260615</t>
         </is>
       </c>
-      <c r="E315" t="n">
+      <c r="E318" t="n">
         <v>3.381408</v>
       </c>
     </row>

--- a/data/MK_ECB_DATA_20260617.xlsx
+++ b/data/MK_ECB_DATA_20260617.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E318"/>
+  <dimension ref="A1:E324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4183,25 +4183,25 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2.709578</v>
+        <v>2.530488</v>
       </c>
     </row>
     <row r="165">
@@ -4220,11 +4220,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2.713377</v>
+        <v>2.709578</v>
       </c>
     </row>
     <row r="166">
@@ -4243,11 +4243,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2.580816</v>
+        <v>2.713377</v>
       </c>
     </row>
     <row r="167">
@@ -4266,11 +4266,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2.563197</v>
+        <v>2.580816</v>
       </c>
     </row>
     <row r="168">
@@ -4289,11 +4289,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2.590769</v>
+        <v>2.563197</v>
       </c>
     </row>
     <row r="169">
@@ -4312,11 +4312,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2.651872</v>
+        <v>2.590769</v>
       </c>
     </row>
     <row r="170">
@@ -4335,11 +4335,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2.734067</v>
+        <v>2.651872</v>
       </c>
     </row>
     <row r="171">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2.720401</v>
+        <v>2.734067</v>
       </c>
     </row>
     <row r="172">
@@ -4381,11 +4381,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2.673633</v>
+        <v>2.720401</v>
       </c>
     </row>
     <row r="173">
@@ -4404,11 +4404,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2.759799</v>
+        <v>2.673633</v>
       </c>
     </row>
     <row r="174">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2.701019</v>
+        <v>2.759799</v>
       </c>
     </row>
     <row r="175">
@@ -4450,11 +4450,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2.758581</v>
+        <v>2.701019</v>
       </c>
     </row>
     <row r="176">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2.732917</v>
+        <v>2.758581</v>
       </c>
     </row>
     <row r="177">
@@ -4496,11 +4496,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2.690643</v>
+        <v>2.732917</v>
       </c>
     </row>
     <row r="178">
@@ -4519,11 +4519,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2.649058</v>
+        <v>2.690643</v>
       </c>
     </row>
     <row r="179">
@@ -4542,11 +4542,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2.550151</v>
+        <v>2.649058</v>
       </c>
     </row>
     <row r="180">
@@ -4565,11 +4565,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2.600158</v>
+        <v>2.550151</v>
       </c>
     </row>
     <row r="181">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2.584193</v>
+        <v>2.600158</v>
       </c>
     </row>
     <row r="182">
@@ -4611,11 +4611,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2.60767</v>
+        <v>2.584193</v>
       </c>
     </row>
     <row r="183">
@@ -4634,11 +4634,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2.573921</v>
+        <v>2.60767</v>
       </c>
     </row>
     <row r="184">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2.664843</v>
+        <v>2.573921</v>
       </c>
     </row>
     <row r="185">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2.631211</v>
+        <v>2.664843</v>
       </c>
     </row>
     <row r="186">
@@ -4703,11 +4703,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2.668913</v>
+        <v>2.631211</v>
       </c>
     </row>
     <row r="187">
@@ -4726,11 +4726,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2.667137</v>
+        <v>2.668913</v>
       </c>
     </row>
     <row r="188">
@@ -4749,11 +4749,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2.690449</v>
+        <v>2.667137</v>
       </c>
     </row>
     <row r="189">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2.70087</v>
+        <v>2.690449</v>
       </c>
     </row>
     <row r="190">
@@ -4795,11 +4795,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2.687806</v>
+        <v>2.70087</v>
       </c>
     </row>
     <row r="191">
@@ -4818,11 +4818,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2.718796</v>
+        <v>2.687806</v>
       </c>
     </row>
     <row r="192">
@@ -4841,11 +4841,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2.687187</v>
+        <v>2.718796</v>
       </c>
     </row>
     <row r="193">
@@ -4864,11 +4864,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2.661527</v>
+        <v>2.687187</v>
       </c>
     </row>
     <row r="194">
@@ -4887,57 +4887,57 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2.585514</v>
+        <v>2.661527</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2.785695</v>
+        <v>2.585514</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2.791931</v>
+        <v>2.586505</v>
       </c>
     </row>
     <row r="197">
@@ -4956,11 +4956,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2.660543</v>
+        <v>2.785695</v>
       </c>
     </row>
     <row r="198">
@@ -4979,11 +4979,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2.647172</v>
+        <v>2.791931</v>
       </c>
     </row>
     <row r="199">
@@ -5002,11 +5002,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2.668906</v>
+        <v>2.660543</v>
       </c>
     </row>
     <row r="200">
@@ -5025,11 +5025,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2.727433</v>
+        <v>2.647172</v>
       </c>
     </row>
     <row r="201">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2.812236</v>
+        <v>2.668906</v>
       </c>
     </row>
     <row r="202">
@@ -5071,11 +5071,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2.800452</v>
+        <v>2.727433</v>
       </c>
     </row>
     <row r="203">
@@ -5094,11 +5094,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2.746714</v>
+        <v>2.812236</v>
       </c>
     </row>
     <row r="204">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2.846863</v>
+        <v>2.800452</v>
       </c>
     </row>
     <row r="205">
@@ -5140,11 +5140,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2.787952</v>
+        <v>2.746714</v>
       </c>
     </row>
     <row r="206">
@@ -5163,11 +5163,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>2.854181</v>
+        <v>2.846863</v>
       </c>
     </row>
     <row r="207">
@@ -5186,11 +5186,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2.823594</v>
+        <v>2.787952</v>
       </c>
     </row>
     <row r="208">
@@ -5209,11 +5209,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>2.775414</v>
+        <v>2.854181</v>
       </c>
     </row>
     <row r="209">
@@ -5232,11 +5232,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>2.73301</v>
+        <v>2.823594</v>
       </c>
     </row>
     <row r="210">
@@ -5255,11 +5255,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2.632702</v>
+        <v>2.775414</v>
       </c>
     </row>
     <row r="211">
@@ -5278,11 +5278,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2.685019</v>
+        <v>2.73301</v>
       </c>
     </row>
     <row r="212">
@@ -5301,11 +5301,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2.665718</v>
+        <v>2.632702</v>
       </c>
     </row>
     <row r="213">
@@ -5324,11 +5324,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>2.685927</v>
+        <v>2.685019</v>
       </c>
     </row>
     <row r="214">
@@ -5347,11 +5347,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2.653732</v>
+        <v>2.665718</v>
       </c>
     </row>
     <row r="215">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>2.737626</v>
+        <v>2.685927</v>
       </c>
     </row>
     <row r="216">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>2.695968</v>
+        <v>2.653732</v>
       </c>
     </row>
     <row r="217">
@@ -5416,11 +5416,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>2.739566</v>
+        <v>2.737626</v>
       </c>
     </row>
     <row r="218">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>2.742955</v>
+        <v>2.695968</v>
       </c>
     </row>
     <row r="219">
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>2.76777</v>
+        <v>2.739566</v>
       </c>
     </row>
     <row r="220">
@@ -5485,11 +5485,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>2.775779</v>
+        <v>2.742955</v>
       </c>
     </row>
     <row r="221">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2.765536</v>
+        <v>2.76777</v>
       </c>
     </row>
     <row r="222">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>2.79679</v>
+        <v>2.775779</v>
       </c>
     </row>
     <row r="223">
@@ -5554,11 +5554,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2.759517</v>
+        <v>2.765536</v>
       </c>
     </row>
     <row r="224">
@@ -5577,11 +5577,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2.740071</v>
+        <v>2.79679</v>
       </c>
     </row>
     <row r="225">
@@ -5600,80 +5600,80 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2.664179</v>
+        <v>2.759517</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>3.000517</v>
+        <v>2.740071</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3.007991</v>
+        <v>2.664179</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2.886073</v>
+        <v>2.660499</v>
       </c>
     </row>
     <row r="229">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>2.876206</v>
+        <v>3.000517</v>
       </c>
     </row>
     <row r="230">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2.889313</v>
+        <v>3.007991</v>
       </c>
     </row>
     <row r="231">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2.939157</v>
+        <v>2.886073</v>
       </c>
     </row>
     <row r="232">
@@ -5761,11 +5761,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>3.015143</v>
+        <v>2.876206</v>
       </c>
     </row>
     <row r="233">
@@ -5784,11 +5784,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>3.012751</v>
+        <v>2.889313</v>
       </c>
     </row>
     <row r="234">
@@ -5807,11 +5807,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>2.955911</v>
+        <v>2.939157</v>
       </c>
     </row>
     <row r="235">
@@ -5830,11 +5830,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>3.063218</v>
+        <v>3.015143</v>
       </c>
     </row>
     <row r="236">
@@ -5853,11 +5853,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>3.014232</v>
+        <v>3.012751</v>
       </c>
     </row>
     <row r="237">
@@ -5876,11 +5876,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3.077971</v>
+        <v>2.955911</v>
       </c>
     </row>
     <row r="238">
@@ -5899,11 +5899,11 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3.044699</v>
+        <v>3.063218</v>
       </c>
     </row>
     <row r="239">
@@ -5922,11 +5922,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2.995816</v>
+        <v>3.014232</v>
       </c>
     </row>
     <row r="240">
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2.948017</v>
+        <v>3.077971</v>
       </c>
     </row>
     <row r="241">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2.848562</v>
+        <v>3.044699</v>
       </c>
     </row>
     <row r="242">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>2.900503</v>
+        <v>2.995816</v>
       </c>
     </row>
     <row r="243">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2.881685</v>
+        <v>2.948017</v>
       </c>
     </row>
     <row r="244">
@@ -6037,11 +6037,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>2.899034</v>
+        <v>2.848562</v>
       </c>
     </row>
     <row r="245">
@@ -6060,11 +6060,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2.869598</v>
+        <v>2.900503</v>
       </c>
     </row>
     <row r="246">
@@ -6083,11 +6083,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>2.942888</v>
+        <v>2.881685</v>
       </c>
     </row>
     <row r="247">
@@ -6106,11 +6106,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>2.892125</v>
+        <v>2.899034</v>
       </c>
     </row>
     <row r="248">
@@ -6129,11 +6129,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>2.936988</v>
+        <v>2.869598</v>
       </c>
     </row>
     <row r="249">
@@ -6152,11 +6152,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>2.946672</v>
+        <v>2.942888</v>
       </c>
     </row>
     <row r="250">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>2.97218</v>
+        <v>2.892125</v>
       </c>
     </row>
     <row r="251">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2.981788</v>
+        <v>2.936988</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2.976278</v>
+        <v>2.946672</v>
       </c>
     </row>
     <row r="253">
@@ -6244,11 +6244,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>3.004347</v>
+        <v>2.97218</v>
       </c>
     </row>
     <row r="254">
@@ -6267,11 +6267,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>2.965561</v>
+        <v>2.981788</v>
       </c>
     </row>
     <row r="255">
@@ -6290,11 +6290,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>2.949891</v>
+        <v>2.976278</v>
       </c>
     </row>
     <row r="256">
@@ -6313,103 +6313,103 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>2.878033</v>
+        <v>3.004347</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>3.228543</v>
+        <v>2.965561</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3.237712</v>
+        <v>2.949891</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>3.119151</v>
+        <v>2.878033</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3.108997</v>
+        <v>2.866621</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3.118124</v>
+        <v>3.228543</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>3.16475</v>
+        <v>3.237712</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>3.237417</v>
+        <v>3.119151</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>3.240594</v>
+        <v>3.108997</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3.18189</v>
+        <v>3.118124</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3.292831</v>
+        <v>3.16475</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>3.250782</v>
+        <v>3.237417</v>
       </c>
     </row>
     <row r="268">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>3.311581</v>
+        <v>3.240594</v>
       </c>
     </row>
     <row r="269">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3.275978</v>
+        <v>3.18189</v>
       </c>
     </row>
     <row r="270">
@@ -6635,11 +6635,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>3.226414</v>
+        <v>3.292831</v>
       </c>
     </row>
     <row r="271">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>3.172951</v>
+        <v>3.250782</v>
       </c>
     </row>
     <row r="272">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>3.070373</v>
+        <v>3.311581</v>
       </c>
     </row>
     <row r="273">
@@ -6704,11 +6704,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>3.121809</v>
+        <v>3.275978</v>
       </c>
     </row>
     <row r="274">
@@ -6727,11 +6727,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>3.104055</v>
+        <v>3.226414</v>
       </c>
     </row>
     <row r="275">
@@ -6750,11 +6750,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>3.12121</v>
+        <v>3.172951</v>
       </c>
     </row>
     <row r="276">
@@ -6773,11 +6773,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3.091758</v>
+        <v>3.070373</v>
       </c>
     </row>
     <row r="277">
@@ -6796,11 +6796,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>3.162397</v>
+        <v>3.121809</v>
       </c>
     </row>
     <row r="278">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>3.105972</v>
+        <v>3.104055</v>
       </c>
     </row>
     <row r="279">
@@ -6842,11 +6842,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>3.150735</v>
+        <v>3.12121</v>
       </c>
     </row>
     <row r="280">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>3.164004</v>
+        <v>3.091758</v>
       </c>
     </row>
     <row r="281">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>3.188864</v>
+        <v>3.162397</v>
       </c>
     </row>
     <row r="282">
@@ -6911,11 +6911,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>3.200686</v>
+        <v>3.105972</v>
       </c>
     </row>
     <row r="283">
@@ -6934,11 +6934,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>3.197992</v>
+        <v>3.150735</v>
       </c>
     </row>
     <row r="284">
@@ -6957,11 +6957,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>3.223329</v>
+        <v>3.164004</v>
       </c>
     </row>
     <row r="285">
@@ -6980,11 +6980,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3.182662</v>
+        <v>3.188864</v>
       </c>
     </row>
     <row r="286">
@@ -7003,11 +7003,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>3.16864</v>
+        <v>3.200686</v>
       </c>
     </row>
     <row r="287">
@@ -7026,126 +7026,126 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>3.096218</v>
+        <v>3.197992</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>3.522383</v>
+        <v>3.223329</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>3.53446</v>
+        <v>3.182662</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>3.419526</v>
+        <v>3.16864</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3.407866</v>
+        <v>3.096218</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>3.414486</v>
+        <v>3.079783</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>3.459084</v>
+        <v>3.522383</v>
       </c>
     </row>
     <row r="294">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>3.532267</v>
+        <v>3.53446</v>
       </c>
     </row>
     <row r="295">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>3.537955</v>
+        <v>3.419526</v>
       </c>
     </row>
     <row r="296">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>3.477861</v>
+        <v>3.407866</v>
       </c>
     </row>
     <row r="297">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>3.591227</v>
+        <v>3.414486</v>
       </c>
     </row>
     <row r="298">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3.555828</v>
+        <v>3.459084</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>3.614122</v>
+        <v>3.532267</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>3.57531</v>
+        <v>3.537955</v>
       </c>
     </row>
     <row r="301">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>3.524301</v>
+        <v>3.477861</v>
       </c>
     </row>
     <row r="302">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>3.465361</v>
+        <v>3.591227</v>
       </c>
     </row>
     <row r="303">
@@ -7394,11 +7394,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>3.358616</v>
+        <v>3.555828</v>
       </c>
     </row>
     <row r="304">
@@ -7417,11 +7417,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>3.408954</v>
+        <v>3.614122</v>
       </c>
     </row>
     <row r="305">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>3.392661</v>
+        <v>3.57531</v>
       </c>
     </row>
     <row r="306">
@@ -7463,11 +7463,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>3.410886</v>
+        <v>3.524301</v>
       </c>
     </row>
     <row r="307">
@@ -7486,11 +7486,11 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>3.380955</v>
+        <v>3.465361</v>
       </c>
     </row>
     <row r="308">
@@ -7509,11 +7509,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>3.450091</v>
+        <v>3.358616</v>
       </c>
     </row>
     <row r="309">
@@ -7532,11 +7532,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>3.390251</v>
+        <v>3.408954</v>
       </c>
     </row>
     <row r="310">
@@ -7555,11 +7555,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3.434872</v>
+        <v>3.392661</v>
       </c>
     </row>
     <row r="311">
@@ -7578,11 +7578,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>3.451103</v>
+        <v>3.410886</v>
       </c>
     </row>
     <row r="312">
@@ -7601,11 +7601,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>3.474414</v>
+        <v>3.380955</v>
       </c>
     </row>
     <row r="313">
@@ -7624,11 +7624,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>3.487726</v>
+        <v>3.450091</v>
       </c>
     </row>
     <row r="314">
@@ -7647,11 +7647,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>3.488064</v>
+        <v>3.390251</v>
       </c>
     </row>
     <row r="315">
@@ -7670,11 +7670,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>3.510348</v>
+        <v>3.434872</v>
       </c>
     </row>
     <row r="316">
@@ -7693,11 +7693,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>3.466867</v>
+        <v>3.451103</v>
       </c>
     </row>
     <row r="317">
@@ -7716,11 +7716,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>3.45513</v>
+        <v>3.474414</v>
       </c>
     </row>
     <row r="318">
@@ -7739,11 +7739,149 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>3.487726</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>10</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>3.488064</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>10</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>3.510348</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>10</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>3.466867</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>10</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>3.45513</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>10</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
           <t>20260615</t>
         </is>
       </c>
-      <c r="E318" t="n">
+      <c r="E323" t="n">
         <v>3.381408</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>10</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>20260616</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>3.360241</v>
       </c>
     </row>
   </sheetData>
